--- a/data/employees/EMP033/AST-EMP033-06.xlsx
+++ b/data/employees/EMP033/AST-EMP033-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment Inventory Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Equipment Inventory Tracker - Taylor Miller (Manufacturing)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Taylor Miller | Role: Architect | Location: Fremont | Date: 2025-02-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>99</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Line ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>OEE %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Downtime (min)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units Produced</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Defect Rate %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>63</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L-01</t>
+          <t>EMP033</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CNC Mill A</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="D5" t="n">
-        <v>12</v>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8</v>
+        <v>70</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L-02</t>
+          <t>EMP033</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Assembly Arm B</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>91</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
+        <v>66</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L-03</t>
+          <t>EMP033</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conveyor Unit C</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>45</v>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
+        <v>65</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L-04</t>
+          <t>EMP033</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Laser Cutter D</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.1</v>
+        <v>97</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>97</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>68</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>61</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>91</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>84</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>74</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>62</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>95</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>69</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>62</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>90</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp033 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>67</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP033</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP033 contributes to ast emp033 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>